--- a/evaluaciones/notas-prueba.xlsx
+++ b/evaluaciones/notas-prueba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebastian\Desktop\PRODUCCION\00. ACCIÓN PROXIMA\03. CUANTI\Curso Cuanti 2\Curso UAH\2025\metodoscuanti2\evaluaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F95CD3B-2CE8-4E36-956F-AF54B3380593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9823FC4E-B34C-4052-B605-AC745624724B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="15196" xr2:uid="{235AF55E-6740-4B55-808E-85BDE9A8A5BF}"/>
+    <workbookView xWindow="68" yWindow="0" windowWidth="16875" windowHeight="10972" xr2:uid="{235AF55E-6740-4B55-808E-85BDE9A8A5BF}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTAS" sheetId="1" r:id="rId1"/>
@@ -759,17 +759,17 @@
         <f t="shared" si="0"/>
         <v>6.4333333333333336</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="16">
+      <c r="I5" s="13">
         <v>0.2</v>
       </c>
+      <c r="J5" s="16"/>
       <c r="K5" s="15">
-        <f t="shared" si="1"/>
-        <v>6.4333333333333336</v>
+        <f>H5+I5</f>
+        <v>6.6333333333333337</v>
       </c>
       <c r="L5" s="15">
         <f>H5+J5</f>
-        <v>6.6333333333333337</v>
+        <v>6.4333333333333336</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
